--- a/099-納品物/020-内部_プログラミング設計/021-クラス図/会員機能/021-クラス図_会員機能_.xlsx
+++ b/099-納品物/020-内部_プログラミング設計/021-クラス図/会員機能/021-クラス図_会員機能_.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\099-納品物\020-内部_プログラミング設計\021-クラス図\会員機能\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\020-内部_プログラミング設計\021-クラス図\会員機能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5677AC48-A6C6-4736-B67B-DDC1EDCE9F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D38CE8-509B-46B7-ABFC-AFF842795410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2808" yWindow="588" windowWidth="17280" windowHeight="10536" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2808" yWindow="396" windowWidth="17280" windowHeight="10536" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="10" r:id="rId1"/>
@@ -180,25 +180,19 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>ショッピング機能：会員機能(購入履歴一覧画面)</t>
+    <t>ショッピング機能：会員機能</t>
     <rPh sb="9" eb="13">
       <t>カイインキノウ</t>
-    </rPh>
-    <rPh sb="14" eb="22">
-      <t>コウニュウリレキイチランガメン</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>ショッピング機能：会員機能（ログイン画面）</t>
+    <t>ショッピング機能：会員機能</t>
     <rPh sb="9" eb="11">
       <t>カイイン</t>
     </rPh>
     <rPh sb="11" eb="13">
       <t>キノウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1130,16 +1124,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>28303</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>89263</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>41555</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>36254</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>119742</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>162490</xdr:rowOff>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>132995</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>76351</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1162,8 +1156,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="583474" y="1308463"/>
-          <a:ext cx="7874725" cy="5396341"/>
+          <a:off x="412616" y="1096428"/>
+          <a:ext cx="7890344" cy="5473488"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14997,12 +14991,12 @@
     <mergeCell ref="X2:AG2"/>
     <mergeCell ref="AH2:AK2"/>
     <mergeCell ref="AL2:AT2"/>
+    <mergeCell ref="AU1:AV2"/>
     <mergeCell ref="A1:S2"/>
     <mergeCell ref="T1:W1"/>
     <mergeCell ref="X1:AG1"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="AL1:AT1"/>
-    <mergeCell ref="AU1:AV2"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.39370078740157483" footer="0.39370078740157483"/>
